--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -72,7 +72,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -278,7 +278,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -484,7 +484,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -690,7 +690,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -896,7 +896,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -1507,7 +1507,7 @@
     <t>939, 940</t>
   </si>
   <si>
-    <t>Date Worked 1</t>
+    <t>Latest Date Worked</t>
   </si>
   <si>
     <t>Reprocessing claim - Confirmation Number: 26119900211</t>
@@ -2113,19 +2113,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>

--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -1073,7 +1073,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="361">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2153,6 +2153,9 @@
   </si>
   <si>
     <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 days</t>
   </si>
 </sst>
 </file>
@@ -4374,12 +4377,12 @@
         <v>-132</v>
       </c>
       <c r="M7" s="14">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>177</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-164</v>
       </c>
       <c r="N7" s="14">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="O7" s="7">
         <v>46119</v>
@@ -4391,10 +4394,10 @@
         <v>89</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T7" s="6" t="s">
         <v>47</v>
@@ -4714,12 +4717,12 @@
         <v>-118</v>
       </c>
       <c r="M10" s="14">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>178</v>
+        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <v>-150</v>
       </c>
       <c r="N10" s="14">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="O10" s="7">
         <v>46133</v>
@@ -4731,10 +4734,10 @@
         <v>89</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>47</v>
@@ -4824,12 +4827,12 @@
         <v>-117</v>
       </c>
       <c r="M11" s="14">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>208</v>
+        <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
+        <v>-149</v>
       </c>
       <c r="N11" s="14">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="O11" s="7">
         <v>46134</v>
@@ -4841,10 +4844,10 @@
         <v>89</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>47</v>
@@ -4940,12 +4943,12 @@
         <v>-112</v>
       </c>
       <c r="M12" s="14">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>242</v>
+        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
+        <v>-144</v>
       </c>
       <c r="N12" s="14">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="O12" s="7">
         <v>46139</v>
@@ -4957,10 +4960,10 @@
         <v>89</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>47</v>
@@ -5170,12 +5173,12 @@
         <v>-110</v>
       </c>
       <c r="M14" s="14">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>180</v>
+        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
+        <v>-142</v>
       </c>
       <c r="N14" s="14">
         <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="O14" s="7">
         <v>46141</v>
@@ -5187,10 +5190,10 @@
         <v>89</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>47</v>
@@ -7632,11 +7635,11 @@
       </c>
       <c r="M8" s="5">
         <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
-        <v>-134</v>
+        <v>-166</v>
       </c>
       <c r="N8" s="5">
-        <f ca="1">IF($C8="","",$C8+60-TODAY())</f>
-        <v>-70</v>
+        <f ca="1">IF($C8="","",$C8+540-TODAY())</f>
+        <v>378</v>
       </c>
       <c r="O8" s="7">
         <v>46117</v>
@@ -7654,7 +7657,7 @@
         <v>142</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>49</v>
@@ -7748,11 +7751,11 @@
       </c>
       <c r="M9" s="5">
         <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
-        <v>-134</v>
+        <v>-166</v>
       </c>
       <c r="N9" s="5">
-        <f ca="1">IF($C9="","",$C9+60-TODAY())</f>
-        <v>-49</v>
+        <f ca="1">IF($C9="","",$C9+540-TODAY())</f>
+        <v>399</v>
       </c>
       <c r="O9" s="7">
         <v>46117</v>
@@ -7770,7 +7773,7 @@
         <v>142</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="U9" s="6" t="s">
         <v>49</v>
@@ -7864,11 +7867,11 @@
       </c>
       <c r="M10" s="5">
         <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
-        <v>-113</v>
+        <v>-145</v>
       </c>
       <c r="N10" s="5">
-        <f ca="1">IF($C10="","",$C10+60-TODAY())</f>
-        <v>-80</v>
+        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <v>368</v>
       </c>
       <c r="O10" s="7">
         <v>46138</v>
@@ -7886,7 +7889,7 @@
         <v>142</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="U10" s="6" t="s">
         <v>49</v>
@@ -8883,9 +8886,9 @@
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-125</v>
       </c>
-      <c r="M6" s="5" t="str">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v/>
+      <c r="M6" s="5">
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-157</v>
       </c>
       <c r="N6" s="5" t="str">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
@@ -8901,10 +8904,10 @@
         <v>89</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>47</v>
@@ -8994,12 +8997,12 @@
         <v>-116</v>
       </c>
       <c r="M7" s="5">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>277</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-148</v>
       </c>
       <c r="N7" s="5">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="O7" s="7">
         <v>46135</v>
@@ -9011,10 +9014,10 @@
         <v>89</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T7" s="6" t="s">
         <v>47</v>
@@ -9110,12 +9113,12 @@
         <v>-116</v>
       </c>
       <c r="M8" s="5">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>166</v>
+        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <v>-148</v>
       </c>
       <c r="N8" s="5">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="O8" s="7">
         <v>46135</v>
@@ -9127,10 +9130,10 @@
         <v>89</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>47</v>
@@ -9657,11 +9660,11 @@
       </c>
       <c r="M2" s="5">
         <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
-        <v>-131</v>
+        <v>-163</v>
       </c>
       <c r="N2" s="5">
-        <f ca="1">IF($C2="","",$C2+60-TODAY())</f>
-        <v>8</v>
+        <f ca="1">IF($C2="","",$C2+540-TODAY())</f>
+        <v>456</v>
       </c>
       <c r="O2" s="7">
         <v>46120</v>
@@ -9679,7 +9682,7 @@
         <v>142</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="U2" s="6" t="s">
         <v>49</v>

--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -230,20 +230,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -433,20 +419,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -642,20 +614,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -848,20 +806,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1051,20 +995,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -3608,7 +3538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO17"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3646,10 +3576,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3770,11 +3699,8 @@
       <c r="AN1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="13" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -3884,11 +3810,8 @@
       <c r="AN2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO2" s="6" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>57</v>
       </c>
@@ -3998,11 +3921,8 @@
       <c r="AN3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>65</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>66</v>
       </c>
@@ -4108,11 +4028,8 @@
       <c r="AN4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO4" s="6" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>57</v>
       </c>
@@ -4222,11 +4139,8 @@
       <c r="AN5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO5" s="6" t="s">
-        <v>77</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
@@ -4336,11 +4250,8 @@
       <c r="AN6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO6" s="6" t="s">
-        <v>86</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>66</v>
       </c>
@@ -4448,11 +4359,8 @@
       <c r="AN7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO7" s="6" t="s">
-        <v>91</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>66</v>
       </c>
@@ -4560,11 +4468,8 @@
       <c r="AN8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>93</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2" t="s">
         <v>66</v>
       </c>
@@ -4674,11 +4579,8 @@
       <c r="AN9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO9" s="6" t="s">
-        <v>100</v>
-      </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:40">
       <c r="A10" s="2" t="s">
         <v>66</v>
       </c>
@@ -4788,11 +4690,8 @@
       <c r="AN10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO10" s="6" t="s">
-        <v>104</v>
-      </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:40">
       <c r="A11" s="2" t="s">
         <v>105</v>
       </c>
@@ -4900,11 +4799,8 @@
       <c r="AN11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO11" s="6" t="s">
-        <v>108</v>
-      </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:40">
       <c r="A12" s="2" t="s">
         <v>109</v>
       </c>
@@ -5014,11 +4910,8 @@
       <c r="AN12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO12" s="6" t="s">
-        <v>114</v>
-      </c>
     </row>
-    <row r="13" spans="1:41">
+    <row r="13" spans="1:40">
       <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
@@ -5130,11 +5023,8 @@
       <c r="AN13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO13" s="6" t="s">
-        <v>118</v>
-      </c>
     </row>
-    <row r="14" spans="1:41">
+    <row r="14" spans="1:40">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
@@ -5244,11 +5134,8 @@
       <c r="AN14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO14" s="6" t="s">
-        <v>123</v>
-      </c>
     </row>
-    <row r="15" spans="1:41">
+    <row r="15" spans="1:40">
       <c r="A15" s="2" t="s">
         <v>124</v>
       </c>
@@ -5358,11 +5245,8 @@
       <c r="AN15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO15" s="6" t="s">
-        <v>132</v>
-      </c>
     </row>
-    <row r="16" spans="1:41">
+    <row r="16" spans="1:40">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -5468,11 +5352,8 @@
       <c r="AN16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO16" s="6" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="17" spans="1:41">
+    <row r="17" spans="1:40">
       <c r="A17" s="2" t="s">
         <v>124</v>
       </c>
@@ -5580,12 +5461,9 @@
       <c r="AN17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO17" s="6" t="s">
-        <v>143</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L17">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -5666,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5703,10 +5581,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -5827,11 +5704,8 @@
       <c r="AN1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="13" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>66</v>
       </c>
@@ -5943,11 +5817,8 @@
       <c r="AN2" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO2" s="6" t="s">
-        <v>157</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4">
@@ -6053,11 +5924,8 @@
       <c r="AN3" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>165</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4">
@@ -6165,11 +6033,8 @@
       <c r="AN4" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO4" s="6" t="s">
-        <v>168</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
@@ -6277,11 +6142,8 @@
       <c r="AN5" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO5" s="6" t="s">
-        <v>171</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
@@ -6391,11 +6253,8 @@
       <c r="AN6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO6" s="6" t="s">
-        <v>177</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>105</v>
       </c>
@@ -6509,11 +6368,8 @@
       <c r="AN7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO7" s="6" t="s">
-        <v>188</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>66</v>
       </c>
@@ -6627,12 +6483,9 @@
       <c r="AN8" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>61</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO8" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN8" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L8">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -6713,7 +6566,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6751,10 +6604,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6875,11 +6727,8 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>105</v>
       </c>
@@ -6995,11 +6844,8 @@
       <c r="AN2" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO2" s="6" t="s">
-        <v>207</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>105</v>
       </c>
@@ -7111,11 +6957,8 @@
       <c r="AN3" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>213</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>66</v>
       </c>
@@ -7233,11 +7076,8 @@
       <c r="AN4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO4" s="6" t="s">
-        <v>219</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>105</v>
       </c>
@@ -7355,11 +7195,8 @@
       <c r="AN5" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO5" s="6" t="s">
-        <v>223</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>105</v>
       </c>
@@ -7477,11 +7314,8 @@
       <c r="AN6" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO6" s="6" t="s">
-        <v>227</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>66</v>
       </c>
@@ -7597,11 +7431,8 @@
       <c r="AN7" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO7" s="6" t="s">
-        <v>232</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4">
@@ -7713,11 +7544,8 @@
       <c r="AN8" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>238</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4">
@@ -7829,11 +7657,8 @@
       <c r="AN9" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO9" s="6" t="s">
-        <v>241</v>
-      </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:40">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4">
@@ -7945,11 +7770,8 @@
       <c r="AN10" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO10" s="6" t="s">
-        <v>244</v>
-      </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:40">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4">
@@ -8061,11 +7883,8 @@
       <c r="AN11" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO11" s="6" t="s">
-        <v>250</v>
-      </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:40">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4">
@@ -8166,12 +7985,9 @@
       <c r="AN12" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AO12" s="6" t="s">
-        <v>258</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO12" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN12" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L12">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -8252,7 +8068,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8290,10 +8106,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8414,11 +8229,8 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -8520,11 +8332,8 @@
       <c r="AN2" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO2" s="6" t="s">
-        <v>264</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>109</v>
       </c>
@@ -8630,11 +8439,8 @@
       <c r="AN3" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>269</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>105</v>
       </c>
@@ -8742,11 +8548,8 @@
       <c r="AN4" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO4" s="6" t="s">
-        <v>273</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4">
@@ -8852,11 +8655,8 @@
       <c r="AN5" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO5" s="6" t="s">
-        <v>279</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -8958,11 +8758,8 @@
       <c r="AN6" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO6" s="6" t="s">
-        <v>283</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>66</v>
       </c>
@@ -9072,11 +8869,8 @@
       <c r="AN7" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO7" s="6" t="s">
-        <v>287</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>66</v>
       </c>
@@ -9184,11 +8978,8 @@
       <c r="AN8" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>290</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4">
@@ -9280,11 +9071,8 @@
       <c r="AN9" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO9" s="6" t="s">
-        <v>298</v>
-      </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:40">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4">
@@ -9372,12 +9160,9 @@
       <c r="AN10" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="AO10" s="6" t="s">
-        <v>304</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO10" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN10" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L10">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -9458,7 +9243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9496,10 +9281,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9620,11 +9404,8 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>109</v>
       </c>
@@ -9730,11 +9511,8 @@
       <c r="AN2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO2" s="6" t="s">
-        <v>309</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
@@ -9838,11 +9616,8 @@
       <c r="AN3" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>315</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>109</v>
       </c>
@@ -9948,11 +9723,8 @@
       <c r="AN4" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO4" s="6" t="s">
-        <v>318</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>109</v>
       </c>
@@ -10064,11 +9836,8 @@
       <c r="AN5" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO5" s="6" t="s">
-        <v>322</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4">
@@ -10174,11 +9943,8 @@
       <c r="AN6" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO6" s="6" t="s">
-        <v>324</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>109</v>
       </c>
@@ -10286,11 +10052,8 @@
       <c r="AN7" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO7" s="6" t="s">
-        <v>329</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4">
@@ -10398,12 +10161,9 @@
       <c r="AN8" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>330</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO8" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN8" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L8">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-01 January - Specialty Claims.xlsx
@@ -1003,7 +1003,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="365">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2086,6 +2086,18 @@
   </si>
   <si>
     <t xml:space="preserve">540 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 claims with a date of service in 2026-01 January, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -10263,7 +10275,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="11" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -10276,12 +10288,12 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="11" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="11" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -10406,7 +10418,7 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="11" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
